--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0001T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0001T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.23638201139268</v>
+        <v>6.863412076851311</v>
       </c>
       <c r="D2" t="n">
-        <v>18.53249978361741</v>
+        <v>3.011531214837829</v>
       </c>
       <c r="E2" t="n">
-        <v>24.22916527534657</v>
+        <v>3.937239357243817</v>
       </c>
       <c r="F2" t="n">
-        <v>16.75170349571273</v>
+        <v>2.722151818053319</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.56024498385048</v>
+        <v>3.341039809875703</v>
       </c>
       <c r="D3" t="n">
-        <v>21.08018039593201</v>
+        <v>3.425529314338952</v>
       </c>
       <c r="E3" t="n">
-        <v>24.22916527534657</v>
+        <v>3.937239357243817</v>
       </c>
       <c r="F3" t="n">
-        <v>16.75170349571273</v>
+        <v>2.722151818053319</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>77.27502611408896</v>
+        <v>12.55719174353946</v>
       </c>
       <c r="D4" t="n">
-        <v>3.947691446462684</v>
+        <v>0.6414998600501861</v>
       </c>
       <c r="E4" t="n">
-        <v>24.22916527534657</v>
+        <v>3.937239357243817</v>
       </c>
       <c r="F4" t="n">
-        <v>16.75170349571273</v>
+        <v>2.722151818053319</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>48.09007131494003</v>
+        <v>7.814636588677756</v>
       </c>
       <c r="D5" t="n">
-        <v>4.610928792893965</v>
+        <v>0.7492759288452694</v>
       </c>
       <c r="E5" t="n">
-        <v>24.22916527534657</v>
+        <v>3.937239357243817</v>
       </c>
       <c r="F5" t="n">
-        <v>16.75170349571273</v>
+        <v>2.722151818053319</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>87.28578215842315</v>
+        <v>14.18393960074376</v>
       </c>
       <c r="D6" t="n">
-        <v>50.09778388490828</v>
+        <v>8.140889881297596</v>
       </c>
       <c r="E6" t="n">
-        <v>24.22916527534657</v>
+        <v>3.937239357243817</v>
       </c>
       <c r="F6" t="n">
-        <v>16.75170349571273</v>
+        <v>2.722151818053319</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
